--- a/05 Others/2026.1 Avaliação Projetos/Turma Python RAD - ARA0095 Turma 3005  SEMI Wyden UniRuy 2026_1.xlsx
+++ b/05 Others/2026.1 Avaliação Projetos/Turma Python RAD - ARA0095 Turma 3005  SEMI Wyden UniRuy 2026_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E10456-11C6-4EC9-9A59-BC74EA86B6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667D1ECB-A626-4CDD-92F6-C32929E65417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD6ED3E7-57DF-4A52-9E4C-63B0F7661B3D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>Falta</t>
   </si>
@@ -78,13 +78,22 @@
   </si>
   <si>
     <t>202503818568 - SAULO VICTOR</t>
+  </si>
+  <si>
+    <t>EQ</t>
+  </si>
+  <si>
+    <t>não fez</t>
+  </si>
+  <si>
+    <t>https://github.com/ArthurPedrada/Se_Ligue_ae</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -111,8 +120,23 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -125,8 +149,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -263,11 +293,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -279,29 +347,40 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -634,108 +713,127 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0212B8F-44EC-4B38-84EB-21D2846DA7CB}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultColWidth="84.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="15"/>
+      <c r="C2" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="9">
+      <c r="E2" s="6">
         <v>0.5</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="10">
-        <f>$B$2/7*4</f>
+      <c r="G2" s="7">
+        <f>$C$2/7*4</f>
         <v>0</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4">
-        <f>F2+G2</f>
+      <c r="H2" s="16">
         <v>0</v>
       </c>
-      <c r="I2" s="5"/>
+      <c r="I2" s="4">
+        <f>G2+H2</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="14">
+        <v>10</v>
+      </c>
+      <c r="C3" s="9">
         <v>0</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="D3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="12">
+      <c r="E3" s="9">
         <v>0.8</v>
       </c>
-      <c r="E3" s="12">
+      <c r="F3" s="9">
         <v>0.3</v>
       </c>
-      <c r="F3" s="13">
-        <f>$B$2/7*4</f>
+      <c r="G3" s="10">
+        <f>$C$2/7*4</f>
         <v>0</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6">
-        <f>F3+G3</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="7"/>
+      <c r="H3" s="5">
+        <v>6</v>
+      </c>
+      <c r="I3" s="5">
+        <f>G3+H3</f>
+        <v>6</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J3" r:id="rId1" xr:uid="{44C37505-89B2-4D9C-ADD0-5225C41A7183}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/05 Others/2026.1 Avaliação Projetos/Turma Python RAD - ARA0095 Turma 3005  SEMI Wyden UniRuy 2026_1.xlsx
+++ b/05 Others/2026.1 Avaliação Projetos/Turma Python RAD - ARA0095 Turma 3005  SEMI Wyden UniRuy 2026_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YduqsArea1\Avaliações Yduqs 2022_2 BDQ 2023_1 2024_2\2026.1 Avaliação Projetos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667D1ECB-A626-4CDD-92F6-C32929E65417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F62CE9-5034-4437-89B8-4CE917CD34D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{DD6ED3E7-57DF-4A52-9E4C-63B0F7661B3D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Falta</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>https://github.com/ArthurPedrada/Se_Ligue_ae</t>
+  </si>
+  <si>
+    <t>https://se-ligue-ae.onrender.com/</t>
   </si>
 </sst>
 </file>
@@ -713,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0212B8F-44EC-4B38-84EB-21D2846DA7CB}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="84.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.42578125" bestFit="1" customWidth="1"/>
@@ -725,9 +728,10 @@
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -759,7 +763,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>11</v>
       </c>
@@ -791,7 +795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
@@ -824,8 +828,11 @@
       <c r="J3" s="17" t="s">
         <v>16</v>
       </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
